--- a/Day- 3 Formulas_Intro.xlsx
+++ b/Day- 3 Formulas_Intro.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\30_Days_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86463E4-839D-4941-B157-B935063F14FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7089F8B2-B4A4-4A6B-B2E6-71A59DC09A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" activeTab="1" xr2:uid="{275B5111-2A81-4A4E-97DC-4D5DAFCE5283}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{275B5111-2A81-4A4E-97DC-4D5DAFCE5283}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="2" r:id="rId1"/>
-    <sheet name="Math_Operators" sheetId="3" r:id="rId2"/>
+    <sheet name="Data" sheetId="5" r:id="rId1"/>
+    <sheet name="Math_Operators" sheetId="6" r:id="rId2"/>
+    <sheet name="Comparison_Operators" sheetId="7" r:id="rId3"/>
+    <sheet name="Cell_Referencing" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
   <si>
     <t>Job Title</t>
   </si>
@@ -158,6 +160,42 @@
   </si>
   <si>
     <t>Concatenation</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>Equal to</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>Greater than</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>Less than</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>Greater than or equal to</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>Less than or equal to</t>
+  </si>
+  <si>
+    <t>&lt;&gt;</t>
+  </si>
+  <si>
+    <t>Not equal to</t>
   </si>
 </sst>
 </file>
@@ -374,7 +412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -430,7 +468,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,26 +799,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3357DA39-EB80-4248-A70D-0F6DC1EFE0B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E9BC3E-BB5D-48B8-8DAB-B8A691A5A6DC}">
   <dimension ref="B1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10" style="3" customWidth="1"/>
+    <col min="7" max="13" width="9" style="3"/>
+    <col min="14" max="14" width="11.21875" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -825,38 +872,6 @@
       <c r="E3" s="9">
         <v>10000</v>
       </c>
-      <c r="F3" s="3">
-        <f>C3</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="3">
-        <f>D3+E3</f>
-        <v>130000</v>
-      </c>
-      <c r="H3" s="23">
-        <f>E3/D3</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="I3" s="3">
-        <f>H3*D3+D3</f>
-        <v>130000</v>
-      </c>
-      <c r="J3" s="3" t="b">
-        <f xml:space="preserve"> I3=G3</f>
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="b">
-        <f>E3&gt;D3</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="3" t="b">
-        <f>$C$15&lt;=F3</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="3" t="b">
-        <f>G3&gt;=$C$16</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
@@ -871,38 +886,6 @@
       <c r="E4" s="9">
         <v>12000</v>
       </c>
-      <c r="F4" s="3">
-        <f t="shared" ref="F4:F12" si="0">C4</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="3">
-        <f t="shared" ref="G4:G12" si="1">D4+E4</f>
-        <v>147000</v>
-      </c>
-      <c r="H4" s="23">
-        <f t="shared" ref="H4:H12" si="2">E4/D4</f>
-        <v>8.8888888888888892E-2</v>
-      </c>
-      <c r="I4" s="3">
-        <f t="shared" ref="I4:I12" si="3">H4*D4+D4</f>
-        <v>147000</v>
-      </c>
-      <c r="J4" s="3" t="b">
-        <f t="shared" ref="J4:J12" si="4" xml:space="preserve"> I4=G4</f>
-        <v>1</v>
-      </c>
-      <c r="K4" s="3" t="b">
-        <f t="shared" ref="K4:K12" si="5">E4&gt;D4</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="b">
-        <f t="shared" ref="L4:L12" si="6">$C$15&lt;=F4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="b">
-        <f t="shared" ref="M4:M12" si="7">G4&gt;=$C$16</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -917,38 +900,6 @@
       <c r="E5" s="9">
         <v>5000</v>
       </c>
-      <c r="F5" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G5" s="3">
-        <f t="shared" si="1"/>
-        <v>80000</v>
-      </c>
-      <c r="H5" s="23">
-        <f t="shared" si="2"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="I5" s="3">
-        <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="J5" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -963,38 +914,6 @@
       <c r="E6" s="9">
         <v>8000</v>
       </c>
-      <c r="F6" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>118000</v>
-      </c>
-      <c r="H6" s="23">
-        <f t="shared" si="2"/>
-        <v>7.2727272727272724E-2</v>
-      </c>
-      <c r="I6" s="3">
-        <f t="shared" si="3"/>
-        <v>118000</v>
-      </c>
-      <c r="J6" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -1009,38 +928,6 @@
       <c r="E7" s="9">
         <v>11000</v>
       </c>
-      <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>136000</v>
-      </c>
-      <c r="H7" s="23">
-        <f t="shared" si="2"/>
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="I7" s="3">
-        <f t="shared" si="3"/>
-        <v>136000</v>
-      </c>
-      <c r="J7" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -1055,38 +942,6 @@
       <c r="E8" s="9">
         <v>7000</v>
       </c>
-      <c r="F8" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>97000</v>
-      </c>
-      <c r="H8" s="23">
-        <f t="shared" si="2"/>
-        <v>7.7777777777777779E-2</v>
-      </c>
-      <c r="I8" s="3">
-        <f t="shared" si="3"/>
-        <v>97000</v>
-      </c>
-      <c r="J8" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K8" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -1101,38 +956,6 @@
       <c r="E9" s="9">
         <v>15000</v>
       </c>
-      <c r="F9" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="1"/>
-        <v>165000</v>
-      </c>
-      <c r="H9" s="23">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="I9" s="3">
-        <f t="shared" si="3"/>
-        <v>165000</v>
-      </c>
-      <c r="J9" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K9" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -1147,38 +970,6 @@
       <c r="E10" s="9">
         <v>13000</v>
       </c>
-      <c r="F10" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>143000</v>
-      </c>
-      <c r="H10" s="23">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="3"/>
-        <v>143000</v>
-      </c>
-      <c r="J10" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K10" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -1193,38 +984,6 @@
       <c r="E11" s="9">
         <v>14000</v>
       </c>
-      <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>154000</v>
-      </c>
-      <c r="H11" s="23">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="3">
-        <f t="shared" si="3"/>
-        <v>154000</v>
-      </c>
-      <c r="J11" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="10" t="s">
@@ -1239,38 +998,6 @@
       <c r="E12" s="12">
         <v>9000</v>
       </c>
-      <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" si="1"/>
-        <v>124000</v>
-      </c>
-      <c r="H12" s="23">
-        <f t="shared" si="2"/>
-        <v>7.8260869565217397E-2</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="3"/>
-        <v>124000</v>
-      </c>
-      <c r="J12" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K12" s="3" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="b">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="3" t="b">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
@@ -1281,17 +1008,13 @@
       <c r="B15" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="19">
-        <v>5</v>
-      </c>
+      <c r="C15" s="19"/>
     </row>
     <row r="16" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="21">
-        <v>90000</v>
-      </c>
+      <c r="C16" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1299,23 +1022,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AE6826-C0A9-4587-A7FB-81849C40D248}">
-  <dimension ref="B1:P12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E053E7-4751-4655-ADA2-5370DBD8B06A}">
+  <dimension ref="B1:L12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="9" width="11" style="3" customWidth="1"/>
+    <col min="10" max="11" width="9" style="3"/>
+    <col min="12" max="12" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:16" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:12" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1340,8 +1065,14 @@
       <c r="I2" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
@@ -1362,22 +1093,22 @@
         <f>D3+E3</f>
         <v>130000</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="24">
         <f>E3/D3</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I3" s="3">
-        <f>H3*D3+D3</f>
+      <c r="I3" s="25">
+        <f>D3+D3*H3</f>
         <v>130000</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1398,22 +1129,22 @@
         <f t="shared" ref="G4:G12" si="1">D4+E4</f>
         <v>147000</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="24">
         <f t="shared" ref="H4:H12" si="2">E4/D4</f>
         <v>8.8888888888888892E-2</v>
       </c>
-      <c r="I4" s="3">
-        <f t="shared" ref="I4:I12" si="3">H4*D4+D4</f>
+      <c r="I4" s="25">
+        <f t="shared" ref="I4:I12" si="3">D4+D4*H4</f>
         <v>147000</v>
       </c>
-      <c r="O4" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K4" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
@@ -1434,22 +1165,22 @@
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="24">
         <f t="shared" si="2"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="25">
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="O5" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1470,22 +1201,22 @@
         <f t="shared" si="1"/>
         <v>118000</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="24">
         <f t="shared" si="2"/>
         <v>7.2727272727272724E-2</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="25">
         <f t="shared" si="3"/>
         <v>118000</v>
       </c>
-      <c r="O6" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1506,22 +1237,22 @@
         <f t="shared" si="1"/>
         <v>136000</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="24">
         <f t="shared" si="2"/>
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="25">
         <f t="shared" si="3"/>
         <v>136000</v>
       </c>
-      <c r="O7" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
@@ -1542,22 +1273,22 @@
         <f t="shared" si="1"/>
         <v>97000</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f t="shared" si="2"/>
         <v>7.7777777777777779E-2</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="25">
         <f t="shared" si="3"/>
         <v>97000</v>
       </c>
-      <c r="O8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
@@ -1578,22 +1309,16 @@
         <f t="shared" si="1"/>
         <v>165000</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="24">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="25">
         <f t="shared" si="3"/>
         <v>165000</v>
       </c>
-      <c r="O9" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1614,16 +1339,16 @@
         <f t="shared" si="1"/>
         <v>143000</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="24">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="25">
         <f t="shared" si="3"/>
         <v>143000</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>12</v>
       </c>
@@ -1644,16 +1369,16 @@
         <f t="shared" si="1"/>
         <v>154000</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="24">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="25">
         <f t="shared" si="3"/>
         <v>154000</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="10" t="s">
         <v>13</v>
       </c>
@@ -1674,13 +1399,1126 @@
         <f t="shared" si="1"/>
         <v>124000</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="24">
         <f t="shared" si="2"/>
         <v>7.8260869565217397E-2</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="25">
         <f t="shared" si="3"/>
         <v>124000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462CCD43-C03F-4DE5-B7D4-B8DA6E363C59}">
+  <dimension ref="B1:N12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="11" style="3" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="3" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="9" style="3"/>
+    <col min="14" max="14" width="19.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:14" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>120000</v>
+      </c>
+      <c r="E3" s="9">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="3">
+        <f>C3</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <f>D3+E3</f>
+        <v>130000</v>
+      </c>
+      <c r="H3" s="24">
+        <f>E3/D3</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="I3" s="25">
+        <f>D3+D3*H3</f>
+        <v>130000</v>
+      </c>
+      <c r="J3" s="3" t="b">
+        <f>G3=I3</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="b">
+        <f>E3&gt;D3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8">
+        <v>135000</v>
+      </c>
+      <c r="E4" s="9">
+        <v>12000</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F12" si="0">C4</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" ref="G4:G12" si="1">D4+E4</f>
+        <v>147000</v>
+      </c>
+      <c r="H4" s="24">
+        <f t="shared" ref="H4:H12" si="2">E4/D4</f>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="I4" s="25">
+        <f t="shared" ref="I4:I12" si="3">D4+D4*H4</f>
+        <v>147000</v>
+      </c>
+      <c r="J4" s="3" t="b">
+        <f t="shared" ref="J4:J12" si="4">G4=I4</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <f t="shared" ref="K4:K12" si="5">E4&gt;D4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8">
+        <v>75000</v>
+      </c>
+      <c r="E5" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="H5" s="24">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I5" s="25">
+        <f t="shared" si="3"/>
+        <v>80000</v>
+      </c>
+      <c r="J5" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8">
+        <v>110000</v>
+      </c>
+      <c r="E6" s="9">
+        <v>8000</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>118000</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="I6" s="25">
+        <f t="shared" si="3"/>
+        <v>118000</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8">
+        <v>125000</v>
+      </c>
+      <c r="E7" s="9">
+        <v>11000</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>136000</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I7" s="25">
+        <f t="shared" si="3"/>
+        <v>136000</v>
+      </c>
+      <c r="J7" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="8">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>90000</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>97000</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="I8" s="25">
+        <f t="shared" si="3"/>
+        <v>97000</v>
+      </c>
+      <c r="J8" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>10</v>
+      </c>
+      <c r="D9" s="8">
+        <v>150000</v>
+      </c>
+      <c r="E9" s="9">
+        <v>15000</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>165000</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="25">
+        <f t="shared" si="3"/>
+        <v>165000</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8">
+        <v>130000</v>
+      </c>
+      <c r="E10" s="9">
+        <v>13000</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="1"/>
+        <v>143000</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="25">
+        <f t="shared" si="3"/>
+        <v>143000</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8">
+        <v>140000</v>
+      </c>
+      <c r="E11" s="9">
+        <v>14000</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="1"/>
+        <v>154000</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="25">
+        <f t="shared" si="3"/>
+        <v>154000</v>
+      </c>
+      <c r="J11" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="11">
+        <v>5</v>
+      </c>
+      <c r="D12" s="11">
+        <v>115000</v>
+      </c>
+      <c r="E12" s="12">
+        <v>9000</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="1"/>
+        <v>124000</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>7.8260869565217397E-2</v>
+      </c>
+      <c r="I12" s="25">
+        <f t="shared" si="3"/>
+        <v>124000</v>
+      </c>
+      <c r="J12" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3776E8-887F-4F3F-9429-130FB1B62B1F}">
+  <dimension ref="B1:O16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="9" width="11" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9" style="3"/>
+    <col min="14" max="14" width="10.44140625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:15" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>120000</v>
+      </c>
+      <c r="E3" s="9">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="3">
+        <f>C3</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <f>D3+E3</f>
+        <v>130000</v>
+      </c>
+      <c r="H3" s="24">
+        <f>E3/D3</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="I3" s="25">
+        <f>D3+D3*H3</f>
+        <v>130000</v>
+      </c>
+      <c r="J3" s="3" t="b">
+        <f>G3=I3</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="b">
+        <f>E3&gt;D3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="b">
+        <f>$C$15&lt;=C3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="b">
+        <f>$G3&gt;=$C$16</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="3">
+        <f>L3*M3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="b">
+        <f>L3*M3=1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8">
+        <v>135000</v>
+      </c>
+      <c r="E4" s="9">
+        <v>12000</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F12" si="0">C4</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" ref="G4:G12" si="1">D4+E4</f>
+        <v>147000</v>
+      </c>
+      <c r="H4" s="24">
+        <f t="shared" ref="H4:H12" si="2">E4/D4</f>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="I4" s="25">
+        <f t="shared" ref="I4:I12" si="3">D4+D4*H4</f>
+        <v>147000</v>
+      </c>
+      <c r="J4" s="3" t="b">
+        <f t="shared" ref="J4:J12" si="4">G4=I4</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <f t="shared" ref="K4:K12" si="5">E4&gt;D4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="b">
+        <f t="shared" ref="L4:L12" si="6">$C$15&lt;=C4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="b">
+        <f t="shared" ref="M4:M12" si="7">$G4&gt;=$C$16</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" ref="N4:N12" si="8">L4*M4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="b">
+        <f t="shared" ref="O4:O12" si="9">L4*M4=1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8">
+        <v>75000</v>
+      </c>
+      <c r="E5" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="H5" s="24">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I5" s="25">
+        <f t="shared" si="3"/>
+        <v>80000</v>
+      </c>
+      <c r="J5" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8">
+        <v>110000</v>
+      </c>
+      <c r="E6" s="9">
+        <v>8000</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>118000</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="I6" s="25">
+        <f t="shared" si="3"/>
+        <v>118000</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8">
+        <v>125000</v>
+      </c>
+      <c r="E7" s="9">
+        <v>11000</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>136000</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I7" s="25">
+        <f t="shared" si="3"/>
+        <v>136000</v>
+      </c>
+      <c r="J7" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="8">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>90000</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>97000</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="I8" s="25">
+        <f t="shared" si="3"/>
+        <v>97000</v>
+      </c>
+      <c r="J8" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>10</v>
+      </c>
+      <c r="D9" s="8">
+        <v>150000</v>
+      </c>
+      <c r="E9" s="9">
+        <v>15000</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>165000</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="25">
+        <f t="shared" si="3"/>
+        <v>165000</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O9" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8">
+        <v>130000</v>
+      </c>
+      <c r="E10" s="9">
+        <v>13000</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="1"/>
+        <v>143000</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="25">
+        <f t="shared" si="3"/>
+        <v>143000</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8">
+        <v>140000</v>
+      </c>
+      <c r="E11" s="9">
+        <v>14000</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="1"/>
+        <v>154000</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="25">
+        <f t="shared" si="3"/>
+        <v>154000</v>
+      </c>
+      <c r="J11" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="11">
+        <v>5</v>
+      </c>
+      <c r="D12" s="11">
+        <v>115000</v>
+      </c>
+      <c r="E12" s="12">
+        <v>9000</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="1"/>
+        <v>124000</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>7.8260869565217397E-2</v>
+      </c>
+      <c r="I12" s="25">
+        <f t="shared" si="3"/>
+        <v>124000</v>
+      </c>
+      <c r="J12" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="3" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="21">
+        <v>90000</v>
       </c>
     </row>
   </sheetData>

--- a/Day- 3 Formulas_Intro.xlsx
+++ b/Day- 3 Formulas_Intro.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7089F8B2-B4A4-4A6B-B2E6-71A59DC09A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{275B5111-2A81-4A4E-97DC-4D5DAFCE5283}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{275B5111-2A81-4A4E-97DC-4D5DAFCE5283}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="5" r:id="rId1"/>
